--- a/PCB/4S六层GaN驱动/生产资料/驱动BOM.xlsx
+++ b/PCB/4S六层GaN驱动/生产资料/驱动BOM.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Union-Projects\DFEx_GT-X2\PCB\4S六层GaN驱动\生产资料\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="29868" windowHeight="15420"/>
   </bookViews>
@@ -90,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="291">
   <si>
     <t>料号</t>
   </si>
@@ -544,7 +549,13 @@
     <t>2KΩ (2001) ±1%</t>
   </si>
   <si>
-    <t>R5, R15, R31</t>
+    <t>R5, R31</t>
+  </si>
+  <si>
+    <t>1.2KΩ (1201) ±1%</t>
+  </si>
+  <si>
+    <t>R15</t>
   </si>
   <si>
     <t>1.5Ω (1R50) ±1%</t>
@@ -553,22 +564,20 @@
     <t>R6, R9, R44, R46</t>
   </si>
   <si>
-    <t>51Ω (51R0) ±1%</t>
+    <t>PTFR0402B51R0N9</t>
+  </si>
+  <si>
+    <t>0402贴片薄膜高精密电阻 51Ω ±0.1% 62.5mW 
+25PPM</t>
   </si>
   <si>
     <t>R7, R43</t>
   </si>
   <si>
-    <t>0.5Ω (0R50) ±5%</t>
-  </si>
-  <si>
-    <t>R8, R45</t>
-  </si>
-  <si>
     <t>0.5Ω (0R50) ±1%</t>
   </si>
   <si>
-    <t>R10, R47</t>
+    <t>R10, R47,R8, R45</t>
   </si>
   <si>
     <t>RT0402BRD0720KL</t>
@@ -2171,7 +2180,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2193,6 +2202,9 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2208,12 +2220,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2227,6 +2233,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2766,10 +2775,10 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -2789,16 +2798,16 @@
       </c>
     </row>
     <row r="2" ht="20.4" spans="1:7">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="2">
@@ -2813,16 +2822,16 @@
       </c>
     </row>
     <row r="3" ht="38.4" spans="1:7">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2">
@@ -2837,16 +2846,16 @@
       </c>
     </row>
     <row r="4" ht="38.4" spans="1:7">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="2">
@@ -2861,16 +2870,16 @@
       </c>
     </row>
     <row r="5" ht="40.8" spans="1:7">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="2">
@@ -2885,16 +2894,16 @@
       </c>
     </row>
     <row r="6" ht="20.4" spans="1:7">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="2">
@@ -2909,16 +2918,16 @@
       </c>
     </row>
     <row r="7" ht="20.4" spans="1:7">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="2">
@@ -2933,16 +2942,16 @@
       </c>
     </row>
     <row r="8" ht="20.4" spans="1:7">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="2">
@@ -2957,16 +2966,16 @@
       </c>
     </row>
     <row r="9" ht="20.4" spans="1:7">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E9" s="2">
@@ -2981,16 +2990,16 @@
       </c>
     </row>
     <row r="10" ht="20.4" spans="1:7">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="2">
@@ -3005,16 +3014,16 @@
       </c>
     </row>
     <row r="11" ht="20.4" spans="1:7">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="2">
@@ -3029,16 +3038,16 @@
       </c>
     </row>
     <row r="12" ht="20.4" spans="1:7">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="14" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="2">
@@ -3053,16 +3062,16 @@
       </c>
     </row>
     <row r="13" ht="20.4" spans="1:7">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="2">
@@ -3077,16 +3086,16 @@
       </c>
     </row>
     <row r="14" ht="20.4" spans="1:7">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="2">
@@ -3101,16 +3110,16 @@
       </c>
     </row>
     <row r="15" ht="40.8" spans="1:7">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="14" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="2">
@@ -3125,16 +3134,16 @@
       </c>
     </row>
     <row r="16" ht="20.4" spans="1:7">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>58</v>
       </c>
       <c r="E16" s="2">
@@ -3149,16 +3158,16 @@
       </c>
     </row>
     <row r="17" ht="40.8" spans="1:7">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="14" t="s">
         <v>54</v>
       </c>
       <c r="E17" s="2">
@@ -3173,16 +3182,16 @@
       </c>
     </row>
     <row r="18" ht="20.4" spans="1:7">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="2">
@@ -3197,16 +3206,16 @@
       </c>
     </row>
     <row r="19" ht="20.4" spans="1:7">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E19" s="2">
@@ -3221,16 +3230,16 @@
       </c>
     </row>
     <row r="20" ht="20.4" spans="1:7">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="2">
@@ -3245,16 +3254,16 @@
       </c>
     </row>
     <row r="21" ht="20.4" spans="1:7">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="14" t="s">
         <v>45</v>
       </c>
       <c r="E21" s="2">
@@ -3269,16 +3278,16 @@
       </c>
     </row>
     <row r="22" ht="20.4" spans="1:7">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="2">
@@ -3293,16 +3302,16 @@
       </c>
     </row>
     <row r="23" ht="20.4" spans="1:7">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="2">
@@ -3317,16 +3326,16 @@
       </c>
     </row>
     <row r="24" ht="20.4" spans="1:7">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="2">
@@ -3341,16 +3350,16 @@
       </c>
     </row>
     <row r="25" ht="20.4" spans="1:7">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="2">
@@ -3365,16 +3374,16 @@
       </c>
     </row>
     <row r="26" ht="20.4" spans="1:7">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E26" s="2">
@@ -3389,16 +3398,16 @@
       </c>
     </row>
     <row r="27" ht="20.4" spans="1:7">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E27" s="2">
@@ -3413,16 +3422,16 @@
       </c>
     </row>
     <row r="28" ht="20.4" spans="1:7">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>87</v>
       </c>
       <c r="E28" s="2">
@@ -3437,16 +3446,16 @@
       </c>
     </row>
     <row r="29" ht="20.4" spans="1:7">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>87</v>
       </c>
       <c r="E29" s="2">
@@ -3461,16 +3470,16 @@
       </c>
     </row>
     <row r="30" ht="20.4" spans="1:7">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>94</v>
       </c>
       <c r="E30" s="2">
@@ -3485,16 +3494,16 @@
       </c>
     </row>
     <row r="31" ht="20.4" spans="1:7">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>98</v>
       </c>
       <c r="E31" s="2">
@@ -3509,16 +3518,16 @@
       </c>
     </row>
     <row r="32" ht="20.4" spans="1:7">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="14" t="s">
         <v>102</v>
       </c>
       <c r="E32" s="2">
@@ -3533,16 +3542,16 @@
       </c>
     </row>
     <row r="33" ht="20.4" spans="1:7">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="14" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="2">
@@ -3557,16 +3566,16 @@
       </c>
     </row>
     <row r="34" ht="38.4" spans="1:7">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="2">
@@ -3581,16 +3590,16 @@
       </c>
     </row>
     <row r="35" ht="20.4" spans="1:7">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="14" t="s">
         <v>112</v>
       </c>
       <c r="E35" s="2">
@@ -3600,21 +3609,21 @@
         <v>0.43</v>
       </c>
       <c r="G35" s="2">
-        <f t="shared" ref="G35:G66" si="1">F35*E35</f>
+        <f>F35*E35</f>
         <v>0.43</v>
       </c>
     </row>
     <row r="36" ht="20.4" spans="1:7">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="14" t="s">
         <v>112</v>
       </c>
       <c r="E36" s="2">
@@ -3624,21 +3633,21 @@
         <v>0.02</v>
       </c>
       <c r="G36" s="2">
-        <f t="shared" si="1"/>
+        <f>F36*E36</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="37" ht="20.4" spans="1:7">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="14" t="s">
         <v>119</v>
       </c>
       <c r="E37" s="2">
@@ -3648,21 +3657,21 @@
         <v>27</v>
       </c>
       <c r="G37" s="2">
-        <f t="shared" si="1"/>
+        <f>F37*E37</f>
         <v>54</v>
       </c>
     </row>
     <row r="38" ht="38.4" spans="1:7">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="14" t="s">
         <v>123</v>
       </c>
       <c r="E38" s="2">
@@ -3672,21 +3681,21 @@
         <v>0.32</v>
       </c>
       <c r="G38" s="2">
-        <f t="shared" si="1"/>
+        <f>F38*E38</f>
         <v>0.64</v>
       </c>
     </row>
     <row r="39" ht="38.4" spans="1:7">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="14" t="s">
         <v>127</v>
       </c>
       <c r="E39" s="2">
@@ -3696,21 +3705,21 @@
         <v>35</v>
       </c>
       <c r="G39" s="2">
-        <f t="shared" si="1"/>
+        <f>F39*E39</f>
         <v>70</v>
       </c>
     </row>
     <row r="40" ht="38.4" spans="1:7">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="14" t="s">
         <v>131</v>
       </c>
       <c r="E40" s="2">
@@ -3720,21 +3729,21 @@
         <v>14.9</v>
       </c>
       <c r="G40" s="2">
-        <f t="shared" si="1"/>
+        <f>F40*E40</f>
         <v>59.6</v>
       </c>
     </row>
     <row r="41" ht="38.4" spans="1:7">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="14" t="s">
         <v>135</v>
       </c>
       <c r="E41" s="2">
@@ -3744,18 +3753,18 @@
         <v>16.33</v>
       </c>
       <c r="G41" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="G41:G46" si="1">F41*E41</f>
         <v>16.33</v>
       </c>
     </row>
     <row r="42" ht="38.4" spans="1:7">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="14" t="s">
         <v>138</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -3773,16 +3782,16 @@
       </c>
     </row>
     <row r="43" ht="20.4" spans="1:7">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E43" s="2">
@@ -3797,16 +3806,16 @@
       </c>
     </row>
     <row r="44" ht="20.4" spans="1:7">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E44" s="2">
@@ -3821,136 +3830,136 @@
       </c>
     </row>
     <row r="45" ht="20.4" spans="1:7">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E45" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" s="2">
         <v>0.03</v>
       </c>
       <c r="G45" s="2">
         <f t="shared" si="1"/>
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="46" ht="20.4" spans="1:7">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E46" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46" s="2">
         <v>0.03</v>
       </c>
       <c r="G46" s="2">
         <f t="shared" si="1"/>
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="47" ht="20.4" spans="1:7">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E47" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" s="2">
         <v>0.03</v>
       </c>
       <c r="G47" s="2">
-        <f t="shared" si="1"/>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="48" ht="20.4" spans="1:7">
-      <c r="A48" s="15" t="s">
+        <f>F47*E47</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="48" ht="38.4" spans="1:7">
+      <c r="A48" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C48" s="15" t="s">
+      <c r="B48" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="C48" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E48" s="2">
         <v>2</v>
       </c>
       <c r="F48" s="2">
-        <v>0.03</v>
+        <v>1.04</v>
       </c>
       <c r="G48" s="2">
-        <f t="shared" si="1"/>
-        <v>0.06</v>
+        <f>F48*E48</f>
+        <v>2.08</v>
       </c>
     </row>
     <row r="49" ht="20.4" spans="1:7">
-      <c r="A49" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B49" s="16" t="s">
+      <c r="A49" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C49" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D49" s="15" t="s">
+      <c r="C49" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E49" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" s="2">
         <v>0.03</v>
       </c>
       <c r="G49" s="2">
-        <f t="shared" si="1"/>
-        <v>0.06</v>
+        <f t="shared" ref="G49:G66" si="2">F49*E49</f>
+        <v>0.12</v>
       </c>
     </row>
     <row r="50" ht="38.4" spans="1:7">
-      <c r="A50" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B50" s="17" t="s">
+      <c r="A50" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="B50" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="C50" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E50" s="2">
@@ -3960,21 +3969,21 @@
         <v>0.58</v>
       </c>
       <c r="G50" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.58</v>
       </c>
     </row>
     <row r="51" ht="20.4" spans="1:7">
-      <c r="A51" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="B51" s="16" t="s">
+      <c r="A51" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D51" s="15" t="s">
+      <c r="C51" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D51" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E51" s="2">
@@ -3984,19 +3993,19 @@
         <v>0.03</v>
       </c>
       <c r="G51" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
     </row>
     <row r="52" ht="38.4" spans="1:7">
-      <c r="A52" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B52" s="17" t="s">
+      <c r="A52" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="B52" s="16" t="s">
         <v>163</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>164</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>139</v>
@@ -4008,21 +4017,21 @@
         <v>0.8</v>
       </c>
       <c r="G52" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="53" ht="38.4" spans="1:7">
-      <c r="A53" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="B53" s="17" t="s">
+      <c r="A53" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="B53" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="C53" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E53" s="2">
@@ -4032,21 +4041,21 @@
         <v>0.17</v>
       </c>
       <c r="G53" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.17</v>
       </c>
     </row>
     <row r="54" ht="20.4" spans="1:7">
-      <c r="A54" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B54" s="16" t="s">
+      <c r="A54" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C54" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="D54" s="15" t="s">
+      <c r="C54" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="D54" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E54" s="2">
@@ -4056,21 +4065,21 @@
         <v>0.03</v>
       </c>
       <c r="G54" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.03</v>
       </c>
     </row>
     <row r="55" ht="38.4" spans="1:7">
-      <c r="A55" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B55" s="17" t="s">
+      <c r="A55" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="B55" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="C55" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E55" s="2">
@@ -4080,21 +4089,21 @@
         <v>0.28</v>
       </c>
       <c r="G55" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28</v>
       </c>
     </row>
     <row r="56" ht="20.4" spans="1:7">
-      <c r="A56" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B56" s="16" t="s">
+      <c r="A56" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C56" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D56" s="15" t="s">
+      <c r="C56" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E56" s="2">
@@ -4104,21 +4113,21 @@
         <v>0.03</v>
       </c>
       <c r="G56" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.18</v>
       </c>
     </row>
     <row r="57" ht="20.4" spans="1:7">
-      <c r="A57" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B57" s="16" t="s">
+      <c r="A57" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="B57" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="C57" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D57" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E57" s="2">
@@ -4128,21 +4137,21 @@
         <v>0.19</v>
       </c>
       <c r="G57" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.19</v>
       </c>
     </row>
     <row r="58" ht="38.4" spans="1:7">
-      <c r="A58" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="B58" s="17" t="s">
+      <c r="A58" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="B58" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="C58" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E58" s="2">
@@ -4152,21 +4161,21 @@
         <v>0.2</v>
       </c>
       <c r="G58" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
     <row r="59" ht="20.4" spans="1:7">
-      <c r="A59" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B59" s="16" t="s">
+      <c r="A59" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="B59" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="C59" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D59" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E59" s="2">
@@ -4176,21 +4185,21 @@
         <v>0.43</v>
       </c>
       <c r="G59" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.43</v>
       </c>
     </row>
     <row r="60" ht="20.4" spans="1:7">
-      <c r="A60" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="B60" s="16" t="s">
+      <c r="A60" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="B60" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="C60" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D60" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E60" s="2">
@@ -4200,21 +4209,21 @@
         <v>0.17</v>
       </c>
       <c r="G60" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.17</v>
       </c>
     </row>
     <row r="61" ht="20.4" spans="1:7">
-      <c r="A61" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B61" s="16" t="s">
+      <c r="A61" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B61" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C61" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="D61" s="15" t="s">
+      <c r="C61" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D61" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E61" s="2">
@@ -4224,21 +4233,21 @@
         <v>0.03</v>
       </c>
       <c r="G61" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.09</v>
       </c>
     </row>
     <row r="62" ht="20.4" spans="1:7">
-      <c r="A62" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="B62" s="16" t="s">
+      <c r="A62" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C62" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="D62" s="15" t="s">
+      <c r="C62" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D62" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E62" s="2">
@@ -4248,21 +4257,21 @@
         <v>0.03</v>
       </c>
       <c r="G62" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.03</v>
       </c>
     </row>
     <row r="63" ht="20.4" spans="1:7">
-      <c r="A63" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="B63" s="16" t="s">
+      <c r="A63" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="B63" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="C63" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E63" s="2">
@@ -4272,21 +4281,21 @@
         <v>0.03</v>
       </c>
       <c r="G63" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.03</v>
       </c>
     </row>
     <row r="64" ht="38.4" spans="1:7">
-      <c r="A64" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="B64" s="17" t="s">
+      <c r="A64" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="B64" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="C64" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E64" s="2">
@@ -4296,21 +4305,21 @@
         <v>0.38</v>
       </c>
       <c r="G64" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.38</v>
       </c>
     </row>
     <row r="65" ht="38.4" spans="1:7">
-      <c r="A65" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="B65" s="17" t="s">
+      <c r="A65" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="B65" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D65" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E65" s="2">
@@ -4320,21 +4329,21 @@
         <v>0.74</v>
       </c>
       <c r="G65" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.74</v>
       </c>
     </row>
     <row r="66" ht="38.4" spans="1:7">
-      <c r="A66" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="B66" s="17" t="s">
+      <c r="A66" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="B66" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="C66" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D66" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E66" s="2">
@@ -4344,22 +4353,22 @@
         <v>0.16</v>
       </c>
       <c r="G66" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="67" ht="20.4" spans="1:7">
-      <c r="A67" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="B67" s="16" t="s">
+      <c r="A67" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B67" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C67" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="D67" s="15" t="s">
+      <c r="C67" s="14" t="s">
         <v>204</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>205</v>
       </c>
       <c r="E67" s="2">
         <v>2</v>
@@ -4368,21 +4377,21 @@
         <v>0.03</v>
       </c>
       <c r="G67" s="2">
-        <f t="shared" ref="G67:G94" si="2">F67*E67</f>
+        <f t="shared" ref="G67:G94" si="3">F67*E67</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="68" ht="20.4" spans="1:7">
-      <c r="A68" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="B68" s="16" t="s">
+      <c r="A68" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C68" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="D68" s="15" t="s">
+      <c r="C68" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D68" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E68" s="2">
@@ -4392,21 +4401,21 @@
         <v>0.03</v>
       </c>
       <c r="G68" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.03</v>
       </c>
     </row>
     <row r="69" ht="20.4" spans="1:7">
-      <c r="A69" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="B69" s="16" t="s">
+      <c r="A69" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C69" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="D69" s="15" t="s">
+      <c r="C69" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D69" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E69" s="2">
@@ -4416,21 +4425,21 @@
         <v>0.03</v>
       </c>
       <c r="G69" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.06</v>
       </c>
     </row>
     <row r="70" ht="38.4" spans="1:7">
-      <c r="A70" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="B70" s="17" t="s">
+      <c r="A70" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="B70" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="C70" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D70" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E70" s="2">
@@ -4440,21 +4449,21 @@
         <v>0.87</v>
       </c>
       <c r="G70" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.87</v>
       </c>
     </row>
     <row r="71" ht="38.4" spans="1:7">
-      <c r="A71" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="B71" s="17" t="s">
+      <c r="A71" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="B71" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="C71" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D71" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E71" s="2">
@@ -4464,21 +4473,21 @@
         <v>0.15</v>
       </c>
       <c r="G71" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="72" ht="20.4" spans="1:7">
-      <c r="A72" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="B72" s="16" t="s">
+      <c r="A72" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B72" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C72" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D72" s="15" t="s">
+      <c r="C72" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="D72" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E72" s="2">
@@ -4488,21 +4497,21 @@
         <v>0.03</v>
       </c>
       <c r="G72" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.06</v>
       </c>
     </row>
     <row r="73" ht="20.4" spans="1:7">
-      <c r="A73" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="B73" s="16" t="s">
+      <c r="A73" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="B73" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="D73" s="15" t="s">
+      <c r="C73" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D73" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E73" s="2">
@@ -4512,21 +4521,21 @@
         <v>0.16</v>
       </c>
       <c r="G73" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="74" ht="38.4" spans="1:7">
-      <c r="A74" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="B74" s="17" t="s">
+      <c r="A74" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="B74" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="C74" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="D74" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E74" s="2">
@@ -4536,21 +4545,21 @@
         <v>0.58</v>
       </c>
       <c r="G74" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.58</v>
       </c>
     </row>
     <row r="75" ht="20.4" spans="1:7">
-      <c r="A75" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="B75" s="16" t="s">
+      <c r="A75" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B75" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C75" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="D75" s="15" t="s">
+      <c r="C75" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D75" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E75" s="2">
@@ -4560,22 +4569,22 @@
         <v>0.03</v>
       </c>
       <c r="G75" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.03</v>
       </c>
     </row>
     <row r="76" ht="38.4" spans="1:7">
-      <c r="A76" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="B76" s="17" t="s">
+      <c r="A76" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="B76" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="C76" s="14" t="s">
         <v>228</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>229</v>
       </c>
       <c r="E76" s="2">
         <v>1</v>
@@ -4584,22 +4593,22 @@
         <v>86</v>
       </c>
       <c r="G76" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>86</v>
       </c>
     </row>
     <row r="77" ht="20.4" spans="1:7">
-      <c r="A77" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="B77" s="16" t="s">
+      <c r="A77" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="B77" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="C77" s="14" t="s">
         <v>232</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>233</v>
       </c>
       <c r="E77" s="2">
         <v>2</v>
@@ -4608,22 +4617,22 @@
         <v>1.55</v>
       </c>
       <c r="G77" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.1</v>
       </c>
     </row>
     <row r="78" ht="38.4" spans="1:7">
-      <c r="A78" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="B78" s="17" t="s">
+      <c r="A78" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="B78" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="C78" s="14" t="s">
         <v>236</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>237</v>
       </c>
       <c r="E78" s="2">
         <v>1</v>
@@ -4632,22 +4641,22 @@
         <v>13.55</v>
       </c>
       <c r="G78" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13.55</v>
       </c>
     </row>
     <row r="79" ht="38.4" spans="1:7">
-      <c r="A79" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="B79" s="17" t="s">
+      <c r="A79" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="B79" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="C79" s="14" t="s">
         <v>240</v>
+      </c>
+      <c r="D79" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="E79" s="2">
         <v>2</v>
@@ -4656,22 +4665,22 @@
         <v>2.16</v>
       </c>
       <c r="G79" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.32</v>
       </c>
     </row>
     <row r="80" ht="38.4" spans="1:7">
-      <c r="A80" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="B80" s="17" t="s">
+      <c r="A80" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="B80" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="D80" s="15" t="s">
+      <c r="C80" s="14" t="s">
         <v>244</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>245</v>
       </c>
       <c r="E80" s="2">
         <v>1</v>
@@ -4680,22 +4689,22 @@
         <v>4.25</v>
       </c>
       <c r="G80" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.25</v>
       </c>
     </row>
     <row r="81" ht="38.4" spans="1:7">
-      <c r="A81" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B81" s="17" t="s">
+      <c r="A81" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="B81" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="D81" s="15" t="s">
-        <v>240</v>
+      <c r="C81" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="E81" s="2">
         <v>1</v>
@@ -4704,22 +4713,22 @@
         <v>5.35</v>
       </c>
       <c r="G81" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.35</v>
       </c>
     </row>
     <row r="82" ht="38.4" spans="1:7">
-      <c r="A82" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="B82" s="17" t="s">
+      <c r="A82" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="B82" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="C82" s="14" t="s">
         <v>251</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="E82" s="2">
         <v>1</v>
@@ -4728,22 +4737,22 @@
         <v>1.13</v>
       </c>
       <c r="G82" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.13</v>
       </c>
     </row>
     <row r="83" ht="38.4" spans="1:7">
-      <c r="A83" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B83" s="17" t="s">
+      <c r="A83" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="B83" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="C83" s="14" t="s">
         <v>255</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>256</v>
       </c>
       <c r="E83" s="2">
         <v>1</v>
@@ -4752,22 +4761,22 @@
         <v>3.63</v>
       </c>
       <c r="G83" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.63</v>
       </c>
     </row>
     <row r="84" ht="38.4" spans="1:7">
-      <c r="A84" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="B84" s="17" t="s">
+      <c r="A84" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="B84" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="D84" s="15" t="s">
-        <v>244</v>
+      <c r="C84" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>245</v>
       </c>
       <c r="E84" s="2">
         <v>1</v>
@@ -4776,22 +4785,22 @@
         <v>1.59</v>
       </c>
       <c r="G84" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.59</v>
       </c>
     </row>
     <row r="85" ht="20.4" spans="1:7">
-      <c r="A85" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="B85" s="16" t="s">
+      <c r="A85" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="B85" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="D85" s="15" t="s">
-        <v>255</v>
+      <c r="C85" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>256</v>
       </c>
       <c r="E85" s="2">
         <v>1</v>
@@ -4800,22 +4809,22 @@
         <v>0.42</v>
       </c>
       <c r="G85" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.42</v>
       </c>
     </row>
     <row r="86" ht="40.8" spans="1:7">
       <c r="A86" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B86" s="7" t="s">
         <v>263</v>
       </c>
+      <c r="B86" s="8" t="s">
+        <v>264</v>
+      </c>
       <c r="C86" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
@@ -4824,22 +4833,22 @@
         <v>0.35</v>
       </c>
       <c r="G86" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.75</v>
       </c>
     </row>
     <row r="87" ht="40.8" spans="1:7">
       <c r="A87" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B87" s="7" t="s">
         <v>267</v>
       </c>
+      <c r="B87" s="8" t="s">
+        <v>268</v>
+      </c>
       <c r="C87" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E87" s="2">
         <v>2</v>
@@ -4848,22 +4857,22 @@
         <v>0.7</v>
       </c>
       <c r="G87" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.4</v>
       </c>
     </row>
     <row r="88" ht="40.8" spans="1:7">
       <c r="A88" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B88" s="7" t="s">
         <v>270</v>
       </c>
+      <c r="B88" s="8" t="s">
+        <v>271</v>
+      </c>
       <c r="C88" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E88" s="2">
         <v>4</v>
@@ -4872,22 +4881,22 @@
         <v>0.42</v>
       </c>
       <c r="G88" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.68</v>
       </c>
     </row>
     <row r="89" ht="40.8" spans="1:7">
       <c r="A89" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B89" s="7" t="s">
         <v>273</v>
       </c>
+      <c r="B89" s="8" t="s">
+        <v>274</v>
+      </c>
       <c r="C89" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E89" s="2">
         <v>2</v>
@@ -4896,22 +4905,22 @@
         <v>0.35</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="90" ht="40.8" spans="1:7">
       <c r="A90" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B90" s="7" t="s">
         <v>276</v>
       </c>
+      <c r="B90" s="8" t="s">
+        <v>277</v>
+      </c>
       <c r="C90" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E90" s="2">
         <v>2</v>
@@ -4920,22 +4929,22 @@
         <v>0.4</v>
       </c>
       <c r="G90" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="91" ht="40.8" spans="1:7">
       <c r="A91" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B91" s="7" t="s">
         <v>279</v>
       </c>
+      <c r="B91" s="8" t="s">
+        <v>280</v>
+      </c>
       <c r="C91" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E91" s="2">
         <v>1</v>
@@ -4944,19 +4953,19 @@
         <v>0.4</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.4</v>
       </c>
     </row>
     <row r="92" ht="198.6" spans="1:7">
       <c r="A92" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B92" s="7" t="s">
         <v>282</v>
       </c>
+      <c r="B92" s="8" t="s">
+        <v>283</v>
+      </c>
       <c r="C92" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D92" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_9EEC4675E0384743873FEC17D11D36C3",1)</f>
@@ -4969,19 +4978,19 @@
         <v>70</v>
       </c>
       <c r="G92" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
     </row>
     <row r="93" ht="122.4" spans="1:7">
       <c r="A93" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B93" s="7" t="s">
         <v>284</v>
       </c>
+      <c r="B93" s="8" t="s">
+        <v>285</v>
+      </c>
       <c r="C93" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D93" s="2" t="str">
         <f>_xlfn.DISPIMG("ID_E8B6F25255D04B3EA6F79DD21AE0765E",1)</f>
@@ -4994,19 +5003,19 @@
         <v>1.1</v>
       </c>
       <c r="G93" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1</v>
       </c>
     </row>
     <row r="94" ht="40.8" spans="1:7">
       <c r="A94" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B94" s="7" t="s">
         <v>286</v>
       </c>
+      <c r="B94" s="8" t="s">
+        <v>287</v>
+      </c>
       <c r="C94" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="2">
@@ -5016,37 +5025,37 @@
         <v>60</v>
       </c>
       <c r="G94" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
     </row>
     <row r="95" ht="20.4" spans="1:7">
-      <c r="A95" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="10">
+      <c r="A95" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B95" s="10"/>
+      <c r="C95" s="10"/>
+      <c r="D95" s="10"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="11">
         <f>SUM(G2:G94)</f>
-        <v>577.04</v>
+        <v>579.06</v>
       </c>
     </row>
     <row r="96" ht="22.2" spans="1:7">
-      <c r="A96" s="11" t="s">
-        <v>289</v>
+      <c r="A96" s="12" t="s">
+        <v>290</v>
       </c>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
       <c r="D96" s="12"/>
-      <c r="E96" s="13">
+      <c r="E96" s="12">
         <f>SUM(E2:E94)</f>
         <v>184</v>
       </c>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
